--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_AMICS CASTELLÓ B.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_AMICS CASTELLÓ B.xlsx
@@ -565,13 +565,13 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>7.7316</v>
+        <v>6.7188</v>
       </c>
       <c r="E2" t="n">
-        <v>5.700200000000001</v>
+        <v>4.2167</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0314</v>
+        <v>2.502</v>
       </c>
       <c r="G2" t="n">
         <v>0.9809999999999999</v>
@@ -610,13 +610,13 @@
         <v>5.4977</v>
       </c>
       <c r="S2" t="n">
-        <v>1.961</v>
+        <v>0.9480999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5604</v>
+        <v>1.077</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5994999999999999</v>
+        <v>-0.1288</v>
       </c>
       <c r="V2" t="n">
         <v>2.4073</v>
@@ -721,13 +721,13 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7747</v>
+        <v>2.3892</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2492</v>
+        <v>0.3837</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5254</v>
+        <v>2.0052</v>
       </c>
       <c r="G4" t="n">
         <v>-0.4711</v>
@@ -766,13 +766,13 @@
         <v>2.5656</v>
       </c>
       <c r="S4" t="n">
-        <v>1.9631</v>
+        <v>0.5775</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0415</v>
+        <v>0.1761</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9216</v>
+        <v>0.4013</v>
       </c>
       <c r="V4" t="n">
         <v>0.6335</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. CONDE BARBERA</t>
+          <t>H. VERNAZA DE LA FUENTE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6217</v>
+        <v>1.5984</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1945</v>
+        <v>0.9225000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8162</v>
+        <v>0.6758999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3804999999999998</v>
+        <v>0.5772999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.0197</v>
+        <v>2.3948</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4003</v>
+        <v>-1.8175</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2184999999999999</v>
+        <v>1.4689</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.177</v>
+        <v>2.7093</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9584999999999999</v>
+        <v>-1.2404</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5989</v>
+        <v>-0.8915999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8427</v>
+        <v>-0.3145</v>
       </c>
       <c r="O5" t="n">
-        <v>1.4417</v>
+        <v>-0.5771000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6493</v>
+        <v>0.5498</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9322</v>
+        <v>-0.9163</v>
       </c>
       <c r="R5" t="n">
-        <v>4.5814</v>
+        <v>1.466</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4819</v>
+        <v>0.4714</v>
       </c>
       <c r="T5" t="n">
-        <v>2.6132</v>
+        <v>0.3699</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.1312</v>
+        <v>0.1014</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.889999999999999</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3428</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.2328</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. SAEZ GIL</t>
+          <t>J. CONDE BARBERA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>1.431100000000002</v>
+        <v>0.7065999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.1872</v>
+        <v>-1.8703</v>
       </c>
       <c r="F6" t="n">
-        <v>5.618399999999999</v>
+        <v>2.577</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.3776</v>
+        <v>0.3804999999999998</v>
       </c>
       <c r="H6" t="n">
-        <v>17.3643</v>
+        <v>-2.0197</v>
       </c>
       <c r="I6" t="n">
-        <v>-18.7419</v>
+        <v>2.4003</v>
       </c>
       <c r="J6" t="n">
-        <v>38.0827</v>
+        <v>-0.2184999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>38.6728</v>
+        <v>-1.177</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5894000000000001</v>
+        <v>0.9584999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-39.4604</v>
+        <v>0.5989</v>
       </c>
       <c r="N6" t="n">
-        <v>-21.3085</v>
+        <v>-0.8427</v>
       </c>
       <c r="O6" t="n">
-        <v>-18.1525</v>
+        <v>1.4417</v>
       </c>
       <c r="P6" t="n">
-        <v>-21.991</v>
+        <v>1.6493</v>
       </c>
       <c r="Q6" t="n">
-        <v>-74.95219999999999</v>
+        <v>-2.9322</v>
       </c>
       <c r="R6" t="n">
-        <v>52.9614</v>
+        <v>4.5814</v>
       </c>
       <c r="S6" t="n">
-        <v>9.917899999999999</v>
+        <v>0.5666999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>3.966599999999999</v>
+        <v>0.9373999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>5.9511</v>
+        <v>-0.3706</v>
       </c>
       <c r="V6" t="n">
-        <v>14.8817</v>
+        <v>-1.889999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>28.715</v>
+        <v>0.3428</v>
       </c>
       <c r="X6" t="n">
-        <v>-13.8332</v>
+        <v>-2.2328</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H. VERNAZA DE LA FUENTE</t>
+          <t>L. MONTANES RUIZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2695</v>
+        <v>0.4971000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7714000000000001</v>
+        <v>-3.6112</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4982</v>
+        <v>4.1084</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5772999999999999</v>
+        <v>-1.8842</v>
       </c>
       <c r="H7" t="n">
-        <v>2.3948</v>
+        <v>-0.5669</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.8175</v>
+        <v>-1.3173</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4689</v>
+        <v>-2.1297</v>
       </c>
       <c r="K7" t="n">
-        <v>2.7093</v>
+        <v>-0.3317000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.2404</v>
+        <v>-1.7981</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8915999999999999</v>
+        <v>0.2456</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3145</v>
+        <v>-0.2351</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5771000000000001</v>
+        <v>0.4807</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5498</v>
+        <v>1.4661</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9163</v>
+        <v>-1.0996</v>
       </c>
       <c r="R7" t="n">
-        <v>1.466</v>
+        <v>2.5656</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1424</v>
+        <v>0.3026</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2187</v>
+        <v>-0.382</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0764</v>
+        <v>0.6846</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.6127</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.6127</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. RAMON CARRION</t>
+          <t>F. CELMA FAYOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4678999999999998</v>
+        <v>0.0594</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5290999999999997</v>
+        <v>-0.1101</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0611</v>
+        <v>0.1695</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5865</v>
+        <v>0.1282</v>
       </c>
       <c r="H8" t="n">
-        <v>2.3912</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1954</v>
+        <v>0.1282</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9501</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2.2417</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7085</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3636</v>
+        <v>0.1282</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1495</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5131</v>
+        <v>0.1282</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8326</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7165999999999999</v>
+        <v>-0.0688</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6576</v>
+        <v>-0.1101</v>
       </c>
       <c r="U8" t="n">
-        <v>0.05890000000000001</v>
+        <v>0.0413</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.835</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-1.2461</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.5889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. CELMA FAYOS</t>
+          <t>J. RAMON CARRION</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0346</v>
+        <v>-0.2853999999999997</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1101</v>
+        <v>0.04820000000000002</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1447</v>
+        <v>-0.3337</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1282</v>
+        <v>2.5865</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2.3912</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1282</v>
+        <v>0.1954</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2.9501</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2.2417</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.7085</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1282</v>
+        <v>-0.3636</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>0.1495</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1282</v>
+        <v>-0.5131</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.8326</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0936</v>
+        <v>-0.0368</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1101</v>
+        <v>0.1768</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0165</v>
+        <v>-0.2136</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-2.835</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-1.2461</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. MONTANES RUIZ</t>
+          <t>M. MONSONIS VICENTE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0633999999999999</v>
+        <v>-1.0937</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.1471</v>
+        <v>-2.2527</v>
       </c>
       <c r="F10" t="n">
-        <v>4.0835</v>
+        <v>1.1592</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.8842</v>
+        <v>-0.03509999999999985</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5669</v>
+        <v>0.6315</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3173</v>
+        <v>-0.6663999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.1297</v>
+        <v>-0.117</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3317000000000001</v>
+        <v>1.0621</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.7981</v>
+        <v>-1.179</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2456</v>
+        <v>0.08199999999999996</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2351</v>
+        <v>-0.4305</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4807</v>
+        <v>0.5125000000000002</v>
       </c>
       <c r="P10" t="n">
-        <v>1.4661</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0996</v>
+        <v>-2.0158</v>
       </c>
       <c r="R10" t="n">
-        <v>2.5656</v>
+        <v>2.0158</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2581</v>
+        <v>-0.7365</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9177999999999999</v>
+        <v>-0.4419</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6597000000000001</v>
+        <v>-0.2947000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6127</v>
+        <v>-0.322</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6127</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7379</v>
+        <v>-1.4104</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2089999999999999</v>
+        <v>-0.1540000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5289</v>
+        <v>-1.2564</v>
       </c>
       <c r="G11" t="n">
         <v>-2.538</v>
@@ -1312,13 +1312,13 @@
         <v>2.1991</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7842000000000001</v>
+        <v>1.1118</v>
       </c>
       <c r="T11" t="n">
-        <v>0.08830000000000005</v>
+        <v>0.1433</v>
       </c>
       <c r="U11" t="n">
-        <v>0.696</v>
+        <v>0.9685</v>
       </c>
       <c r="V11" t="n">
         <v>-1.267</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. MONSONIS VICENTE</t>
+          <t>P. RODRIGUEZ SALVA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.4177</v>
+        <v>-2.5589</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0771</v>
+        <v>-3.3703</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6594</v>
+        <v>0.8114</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.03509999999999985</v>
+        <v>-1.6013</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6315</v>
+        <v>-0.457</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6663999999999999</v>
+        <v>-1.1443</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.117</v>
+        <v>-1.1754</v>
       </c>
       <c r="K12" t="n">
-        <v>1.0621</v>
+        <v>0.065</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.179</v>
+        <v>-1.2404</v>
       </c>
       <c r="M12" t="n">
-        <v>0.08199999999999996</v>
+        <v>-0.4259</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4305</v>
+        <v>-0.522</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5125000000000002</v>
+        <v>0.0961</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q12" t="n">
         <v>-2.0158</v>
       </c>
       <c r="R12" t="n">
-        <v>2.0158</v>
+        <v>0.733</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.0607</v>
+        <v>-0.2979</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2662</v>
+        <v>-0.1791</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7945</v>
+        <v>-0.1188</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.322</v>
+        <v>0.6231</v>
       </c>
       <c r="W12" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.6439</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ SALVA</t>
+          <t>D. SAEZ GIL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.7046</v>
+        <v>-3.035299999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.4664</v>
+        <v>-7.4264</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7618</v>
+        <v>4.391300000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.6013</v>
+        <v>-1.3776</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.457</v>
+        <v>17.3643</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.1443</v>
+        <v>-18.7419</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.1754</v>
+        <v>38.0827</v>
       </c>
       <c r="K13" t="n">
-        <v>0.065</v>
+        <v>38.6728</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.2404</v>
+        <v>-0.5894000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.4259</v>
+        <v>-39.4604</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.522</v>
+        <v>-21.3085</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0961</v>
+        <v>-18.1525</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.2828</v>
+        <v>-21.991</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.0158</v>
+        <v>-74.95219999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>0.733</v>
+        <v>52.9614</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4436</v>
+        <v>5.4512</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2753</v>
+        <v>0.7274000000000002</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1683</v>
+        <v>4.7235</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6231</v>
+        <v>14.8817</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>28.715</v>
       </c>
       <c r="X13" t="n">
-        <v>0.6231</v>
+        <v>-13.8332</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F. TORCOLETTI</t>
+          <t>J. MARIA VENTURA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.399900000000001</v>
+        <v>-5.9081</v>
       </c>
       <c r="E14" t="n">
-        <v>-14.0802</v>
+        <v>-0.9517000000000013</v>
       </c>
       <c r="F14" t="n">
-        <v>7.680599999999999</v>
+        <v>-4.956799999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-7.601000000000001</v>
+        <v>-7.7532</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3336</v>
+        <v>-7.9256</v>
       </c>
       <c r="I14" t="n">
-        <v>-9.934799999999999</v>
+        <v>0.1729000000000002</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.3627</v>
+        <v>2.5967</v>
       </c>
       <c r="K14" t="n">
-        <v>10.6082</v>
+        <v>1.267</v>
       </c>
       <c r="L14" t="n">
-        <v>-13.9708</v>
+        <v>1.3297</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.238300000000001</v>
+        <v>-10.3502</v>
       </c>
       <c r="N14" t="n">
-        <v>-8.2744</v>
+        <v>-9.193</v>
       </c>
       <c r="O14" t="n">
-        <v>4.0358</v>
+        <v>-1.1573</v>
       </c>
       <c r="P14" t="n">
-        <v>2.931999999999999</v>
+        <v>16.4931</v>
       </c>
       <c r="Q14" t="n">
-        <v>-22.3574</v>
+        <v>-5.3146</v>
       </c>
       <c r="R14" t="n">
-        <v>25.2894</v>
+        <v>21.8076</v>
       </c>
       <c r="S14" t="n">
-        <v>6.652000000000001</v>
+        <v>-4.4395</v>
       </c>
       <c r="T14" t="n">
-        <v>6.5093</v>
+        <v>-2.0452</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1424</v>
+        <v>-2.3939</v>
       </c>
       <c r="V14" t="n">
-        <v>-8.3828</v>
+        <v>-10.2086</v>
       </c>
       <c r="W14" t="n">
-        <v>5.1302</v>
+        <v>3.8114</v>
       </c>
       <c r="X14" t="n">
-        <v>-13.5131</v>
+        <v>-14.0198</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. LARA BARRACHINA</t>
+          <t>A. BALADA SEGOVIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>-7.138999999999998</v>
+        <v>-6.2827</v>
       </c>
       <c r="E15" t="n">
-        <v>-7.351500000000001</v>
+        <v>-3.7315</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2121000000000002</v>
+        <v>-2.5513</v>
       </c>
       <c r="G15" t="n">
-        <v>-26.4764</v>
+        <v>-6.3012</v>
       </c>
       <c r="H15" t="n">
-        <v>-15.9216</v>
+        <v>-0.8688</v>
       </c>
       <c r="I15" t="n">
-        <v>-10.5551</v>
+        <v>-5.4324</v>
       </c>
       <c r="J15" t="n">
-        <v>26.6636</v>
+        <v>-2.0934</v>
       </c>
       <c r="K15" t="n">
-        <v>14.4811</v>
+        <v>2.7612</v>
       </c>
       <c r="L15" t="n">
-        <v>12.1823</v>
+        <v>-4.8548</v>
       </c>
       <c r="M15" t="n">
-        <v>-53.1404</v>
+        <v>-4.2077</v>
       </c>
       <c r="N15" t="n">
-        <v>-30.4029</v>
+        <v>-3.6301</v>
       </c>
       <c r="O15" t="n">
-        <v>-22.7377</v>
+        <v>-0.5776999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>-6.5975</v>
+        <v>-0.1832</v>
       </c>
       <c r="Q15" t="n">
-        <v>-68.90470000000001</v>
+        <v>-5.681</v>
       </c>
       <c r="R15" t="n">
-        <v>62.3076</v>
+        <v>5.4977</v>
       </c>
       <c r="S15" t="n">
-        <v>33.4655</v>
+        <v>-0.4631</v>
       </c>
       <c r="T15" t="n">
-        <v>14.887</v>
+        <v>-0.4226000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>18.5784</v>
+        <v>-0.0404</v>
       </c>
       <c r="V15" t="n">
-        <v>-7.5308</v>
+        <v>0.6648000000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>20.0021</v>
+        <v>4.4657</v>
       </c>
       <c r="X15" t="n">
-        <v>-27.533</v>
+        <v>-3.8009</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. BALADA SEGOVIA</t>
+          <t>P. BALAGUER BARBA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D16" t="n">
-        <v>-7.3629</v>
+        <v>-8.0365</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.762</v>
+        <v>-4.894400000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.6009</v>
+        <v>-3.1419</v>
       </c>
       <c r="G16" t="n">
-        <v>-6.3012</v>
+        <v>-0.8878000000000013</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8688</v>
+        <v>1.694900000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-5.4324</v>
+        <v>-2.5826</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.0934</v>
+        <v>7.8643</v>
       </c>
       <c r="K16" t="n">
-        <v>2.7612</v>
+        <v>6.4702</v>
       </c>
       <c r="L16" t="n">
-        <v>-4.8548</v>
+        <v>1.393899999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-4.2077</v>
+        <v>-8.751899999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>-3.6301</v>
+        <v>-4.775300000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5776999999999999</v>
+        <v>-3.9769</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.1832</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q16" t="n">
-        <v>-5.681</v>
+        <v>-13.9277</v>
       </c>
       <c r="R16" t="n">
-        <v>5.4977</v>
+        <v>13.561</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5432</v>
+        <v>-6.3334</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.4532</v>
+        <v>-3.6291</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.08990000000000001</v>
+        <v>-2.7044</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6648000000000001</v>
+        <v>-0.4485000000000002</v>
       </c>
       <c r="W16" t="n">
-        <v>4.4657</v>
+        <v>4.7979</v>
       </c>
       <c r="X16" t="n">
-        <v>-3.8009</v>
+        <v>-5.2464</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>-11.0632</v>
+        <v>-8.7873</v>
       </c>
       <c r="E17" t="n">
-        <v>-4.3636</v>
+        <v>-2.9344</v>
       </c>
       <c r="F17" t="n">
-        <v>-6.6994</v>
+        <v>-5.8529</v>
       </c>
       <c r="G17" t="n">
         <v>-7.9639</v>
@@ -1780,13 +1780,13 @@
         <v>6.7807</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.0708</v>
+        <v>0.2051</v>
       </c>
       <c r="T17" t="n">
-        <v>-2.187</v>
+        <v>-0.7577999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1161999999999999</v>
+        <v>0.9627</v>
       </c>
       <c r="V17" t="n">
         <v>-4.1437</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. BALAGUER BARBA</t>
+          <t>F. TORCOLETTI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,70 +1810,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D18" t="n">
-        <v>-11.696</v>
+        <v>-11.2461</v>
       </c>
       <c r="E18" t="n">
-        <v>-6.667199999999999</v>
+        <v>-18.7498</v>
       </c>
       <c r="F18" t="n">
-        <v>-5.029</v>
+        <v>7.504</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8878000000000013</v>
+        <v>-7.601000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>1.694900000000001</v>
+        <v>2.3336</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.5826</v>
+        <v>-9.934799999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>7.8643</v>
+        <v>-3.3627</v>
       </c>
       <c r="K18" t="n">
-        <v>6.4702</v>
+        <v>10.6082</v>
       </c>
       <c r="L18" t="n">
-        <v>1.393899999999999</v>
+        <v>-13.9708</v>
       </c>
       <c r="M18" t="n">
-        <v>-8.751899999999999</v>
+        <v>-4.238300000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>-4.775300000000001</v>
+        <v>-8.2744</v>
       </c>
       <c r="O18" t="n">
-        <v>-3.9769</v>
+        <v>4.0358</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3665</v>
+        <v>2.931999999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>-13.9277</v>
+        <v>-22.3574</v>
       </c>
       <c r="R18" t="n">
-        <v>13.561</v>
+        <v>25.2894</v>
       </c>
       <c r="S18" t="n">
-        <v>-9.9933</v>
+        <v>1.8058</v>
       </c>
       <c r="T18" t="n">
-        <v>-5.4019</v>
+        <v>1.84</v>
       </c>
       <c r="U18" t="n">
-        <v>-4.5915</v>
+        <v>-0.03389999999999993</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.4485000000000002</v>
+        <v>-8.3828</v>
       </c>
       <c r="W18" t="n">
-        <v>4.7979</v>
+        <v>5.1302</v>
       </c>
       <c r="X18" t="n">
-        <v>-5.2464</v>
+        <v>-13.5131</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>-14.5084</v>
+        <v>-11.7448</v>
       </c>
       <c r="E19" t="n">
-        <v>-11.3869</v>
+        <v>-9.6972</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.1219</v>
+        <v>-2.0474</v>
       </c>
       <c r="G19" t="n">
         <v>-5.8241</v>
@@ -1936,13 +1936,13 @@
         <v>10.4458</v>
       </c>
       <c r="S19" t="n">
-        <v>-7.3538</v>
+        <v>-4.5904</v>
       </c>
       <c r="T19" t="n">
-        <v>-3.9489</v>
+        <v>-2.259</v>
       </c>
       <c r="U19" t="n">
-        <v>-3.4054</v>
+        <v>-2.3315</v>
       </c>
       <c r="V19" t="n">
         <v>-3.346</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. MARIA VENTURA</t>
+          <t>J. TALLON GUIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,76 +1966,76 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D20" t="n">
-        <v>-15.9573</v>
+        <v>-12.0182</v>
       </c>
       <c r="E20" t="n">
-        <v>-6.295999999999999</v>
+        <v>-7.0588</v>
       </c>
       <c r="F20" t="n">
-        <v>-9.6616</v>
+        <v>-4.9594</v>
       </c>
       <c r="G20" t="n">
-        <v>-7.7532</v>
+        <v>-5.3849</v>
       </c>
       <c r="H20" t="n">
-        <v>-7.9256</v>
+        <v>-0.6468999999999998</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1729000000000002</v>
+        <v>-4.738099999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>2.5967</v>
+        <v>8.186400000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>1.267</v>
+        <v>6.317900000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3297</v>
+        <v>1.868400000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-10.3502</v>
+        <v>-13.5712</v>
       </c>
       <c r="N20" t="n">
-        <v>-9.193</v>
+        <v>-6.9646</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1573</v>
+        <v>-6.6066</v>
       </c>
       <c r="P20" t="n">
-        <v>16.4931</v>
+        <v>4.2149</v>
       </c>
       <c r="Q20" t="n">
-        <v>-5.3146</v>
+        <v>-18.1427</v>
       </c>
       <c r="R20" t="n">
-        <v>21.8076</v>
+        <v>22.3573</v>
       </c>
       <c r="S20" t="n">
-        <v>-14.4889</v>
+        <v>-4.0646</v>
       </c>
       <c r="T20" t="n">
-        <v>-7.3896</v>
+        <v>-2.8353</v>
       </c>
       <c r="U20" t="n">
-        <v>-7.0991</v>
+        <v>-1.2294</v>
       </c>
       <c r="V20" t="n">
-        <v>-10.2086</v>
+        <v>-6.7836</v>
       </c>
       <c r="W20" t="n">
-        <v>3.8114</v>
+        <v>5.7326</v>
       </c>
       <c r="X20" t="n">
-        <v>-14.0198</v>
+        <v>-12.5161</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. TALLON GUIA</t>
+          <t>B. KABASELE KATUMBA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2044,76 +2044,76 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D21" t="n">
-        <v>-17.9943</v>
+        <v>-20.0581</v>
       </c>
       <c r="E21" t="n">
-        <v>-10.6585</v>
+        <v>-11.4854</v>
       </c>
       <c r="F21" t="n">
-        <v>-7.335599999999999</v>
+        <v>-8.572800000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>-5.3849</v>
+        <v>-14.0572</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6468999999999998</v>
+        <v>-9.5002</v>
       </c>
       <c r="I21" t="n">
-        <v>-4.738099999999999</v>
+        <v>-4.557</v>
       </c>
       <c r="J21" t="n">
-        <v>8.186400000000001</v>
+        <v>-4.3487</v>
       </c>
       <c r="K21" t="n">
-        <v>6.317900000000001</v>
+        <v>-4.7953</v>
       </c>
       <c r="L21" t="n">
-        <v>1.868400000000001</v>
+        <v>0.4461000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>-13.5712</v>
+        <v>-9.708600000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>-6.9646</v>
+        <v>-4.705299999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>-6.6066</v>
+        <v>-5.0033</v>
       </c>
       <c r="P21" t="n">
-        <v>4.2149</v>
+        <v>-0.5498999999999999</v>
       </c>
       <c r="Q21" t="n">
-        <v>-18.1427</v>
+        <v>-13.3779</v>
       </c>
       <c r="R21" t="n">
-        <v>22.3573</v>
+        <v>12.8279</v>
       </c>
       <c r="S21" t="n">
-        <v>-10.0406</v>
+        <v>-0.1838000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-6.435</v>
+        <v>-1.3812</v>
       </c>
       <c r="U21" t="n">
-        <v>-3.6059</v>
+        <v>1.1977</v>
       </c>
       <c r="V21" t="n">
-        <v>-6.7836</v>
+        <v>-5.267300000000001</v>
       </c>
       <c r="W21" t="n">
-        <v>5.7326</v>
+        <v>7.6226</v>
       </c>
       <c r="X21" t="n">
-        <v>-12.5161</v>
+        <v>-12.8901</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B. KABASELE KATUMBA</t>
+          <t>M. CALANCHE GONZALEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2122,76 +2122,76 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D22" t="n">
-        <v>-23.0464</v>
+        <v>-25.2596</v>
       </c>
       <c r="E22" t="n">
-        <v>-12.3378</v>
+        <v>-17.8166</v>
       </c>
       <c r="F22" t="n">
-        <v>-10.7089</v>
+        <v>-7.443</v>
       </c>
       <c r="G22" t="n">
-        <v>-14.0572</v>
+        <v>-14.1829</v>
       </c>
       <c r="H22" t="n">
-        <v>-9.5002</v>
+        <v>-3.3475</v>
       </c>
       <c r="I22" t="n">
-        <v>-4.557</v>
+        <v>-10.8354</v>
       </c>
       <c r="J22" t="n">
-        <v>-4.3487</v>
+        <v>-0.8742000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.7953</v>
+        <v>4.4133</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4461000000000001</v>
+        <v>-5.2873</v>
       </c>
       <c r="M22" t="n">
-        <v>-9.708600000000001</v>
+        <v>-13.3086</v>
       </c>
       <c r="N22" t="n">
-        <v>-4.705299999999999</v>
+        <v>-7.760800000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>-5.0033</v>
+        <v>-5.548</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.5498999999999999</v>
+        <v>-4.398000000000001</v>
       </c>
       <c r="Q22" t="n">
-        <v>-13.3779</v>
+        <v>-20.1584</v>
       </c>
       <c r="R22" t="n">
-        <v>12.8279</v>
+        <v>15.7602</v>
       </c>
       <c r="S22" t="n">
-        <v>-3.172</v>
+        <v>-2.7614</v>
       </c>
       <c r="T22" t="n">
-        <v>-2.2337</v>
+        <v>-1.5926</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9383</v>
+        <v>-1.1688</v>
       </c>
       <c r="V22" t="n">
-        <v>-5.267300000000001</v>
+        <v>-3.9174</v>
       </c>
       <c r="W22" t="n">
-        <v>7.6226</v>
+        <v>4.8083</v>
       </c>
       <c r="X22" t="n">
-        <v>-12.8901</v>
+        <v>-8.7257</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. CALANCHE GONZALEZ</t>
+          <t>J. TORRES HERNANDO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2200,76 +2200,76 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D23" t="n">
-        <v>-28.8805</v>
+        <v>-29.3294</v>
       </c>
       <c r="E23" t="n">
-        <v>-19.1907</v>
+        <v>-14.8545</v>
       </c>
       <c r="F23" t="n">
-        <v>-9.690000000000001</v>
+        <v>-14.4747</v>
       </c>
       <c r="G23" t="n">
-        <v>-14.1829</v>
+        <v>-50.6732</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.3475</v>
+        <v>-26.3819</v>
       </c>
       <c r="I23" t="n">
-        <v>-10.8354</v>
+        <v>-24.2918</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8742000000000001</v>
+        <v>-11.1778</v>
       </c>
       <c r="K23" t="n">
-        <v>4.4133</v>
+        <v>-4.7479</v>
       </c>
       <c r="L23" t="n">
-        <v>-5.2873</v>
+        <v>-6.429899999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-13.3086</v>
+        <v>-39.4955</v>
       </c>
       <c r="N23" t="n">
-        <v>-7.760800000000001</v>
+        <v>-21.6342</v>
       </c>
       <c r="O23" t="n">
-        <v>-5.548</v>
+        <v>-17.8613</v>
       </c>
       <c r="P23" t="n">
-        <v>-4.398000000000001</v>
+        <v>26.9389</v>
       </c>
       <c r="Q23" t="n">
-        <v>-20.1584</v>
+        <v>-13.1948</v>
       </c>
       <c r="R23" t="n">
-        <v>15.7602</v>
+        <v>40.1336</v>
       </c>
       <c r="S23" t="n">
-        <v>-6.3823</v>
+        <v>-8.9885</v>
       </c>
       <c r="T23" t="n">
-        <v>-2.9665</v>
+        <v>-5.1356</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.4157</v>
+        <v>-3.8528</v>
       </c>
       <c r="V23" t="n">
-        <v>-3.9174</v>
+        <v>3.3939</v>
       </c>
       <c r="W23" t="n">
-        <v>4.8083</v>
+        <v>14.6536</v>
       </c>
       <c r="X23" t="n">
-        <v>-8.7257</v>
+        <v>-11.2596</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. TORRES HERNANDO</t>
+          <t>M. LARA BARRACHINA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2278,76 +2278,76 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D24" t="n">
-        <v>-43.4121</v>
+        <v>-30.0422</v>
       </c>
       <c r="E24" t="n">
-        <v>-24.843</v>
+        <v>-19.6425</v>
       </c>
       <c r="F24" t="n">
-        <v>-18.5691</v>
+        <v>-10.4</v>
       </c>
       <c r="G24" t="n">
-        <v>-50.6732</v>
+        <v>-26.4764</v>
       </c>
       <c r="H24" t="n">
-        <v>-26.3819</v>
+        <v>-15.9216</v>
       </c>
       <c r="I24" t="n">
-        <v>-24.2918</v>
+        <v>-10.5551</v>
       </c>
       <c r="J24" t="n">
-        <v>-11.1778</v>
+        <v>26.6636</v>
       </c>
       <c r="K24" t="n">
-        <v>-4.7479</v>
+        <v>14.4811</v>
       </c>
       <c r="L24" t="n">
-        <v>-6.429899999999999</v>
+        <v>12.1823</v>
       </c>
       <c r="M24" t="n">
-        <v>-39.4955</v>
+        <v>-53.1404</v>
       </c>
       <c r="N24" t="n">
-        <v>-21.6342</v>
+        <v>-30.4029</v>
       </c>
       <c r="O24" t="n">
-        <v>-17.8613</v>
+        <v>-22.7377</v>
       </c>
       <c r="P24" t="n">
-        <v>26.9389</v>
+        <v>-6.5975</v>
       </c>
       <c r="Q24" t="n">
-        <v>-13.1948</v>
+        <v>-68.90470000000001</v>
       </c>
       <c r="R24" t="n">
-        <v>40.1336</v>
+        <v>62.3076</v>
       </c>
       <c r="S24" t="n">
-        <v>-23.0715</v>
+        <v>10.5625</v>
       </c>
       <c r="T24" t="n">
-        <v>-15.1239</v>
+        <v>2.596</v>
       </c>
       <c r="U24" t="n">
-        <v>-7.9473</v>
+        <v>7.9663</v>
       </c>
       <c r="V24" t="n">
-        <v>3.3939</v>
+        <v>-7.5308</v>
       </c>
       <c r="W24" t="n">
-        <v>14.6536</v>
+        <v>20.0021</v>
       </c>
       <c r="X24" t="n">
-        <v>-11.2596</v>
+        <v>-27.533</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>L. GARCIA JIMENEZ</t>
+          <t>J. BALFAGON MIRAVET</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2356,76 +2356,76 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D25" t="n">
-        <v>-51.599</v>
+        <v>-48.0293</v>
       </c>
       <c r="E25" t="n">
-        <v>-44.283</v>
+        <v>-31.8329</v>
       </c>
       <c r="F25" t="n">
-        <v>-7.3161</v>
+        <v>-16.1959</v>
       </c>
       <c r="G25" t="n">
-        <v>-27.5519</v>
+        <v>-7.4504</v>
       </c>
       <c r="H25" t="n">
-        <v>-21.4893</v>
+        <v>-3.6948</v>
       </c>
       <c r="I25" t="n">
-        <v>-6.062899999999999</v>
+        <v>-3.755</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.056999999999999</v>
+        <v>37.6355</v>
       </c>
       <c r="K25" t="n">
-        <v>-5.039</v>
+        <v>22.3086</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.018</v>
+        <v>15.3269</v>
       </c>
       <c r="M25" t="n">
-        <v>-20.4953</v>
+        <v>-45.0856</v>
       </c>
       <c r="N25" t="n">
-        <v>-16.4501</v>
+        <v>-26.0036</v>
       </c>
       <c r="O25" t="n">
-        <v>-4.045100000000001</v>
+        <v>-19.0821</v>
       </c>
       <c r="P25" t="n">
-        <v>-11.3619</v>
+        <v>-33.5361</v>
       </c>
       <c r="Q25" t="n">
-        <v>-45.0815</v>
+        <v>-88.8796</v>
       </c>
       <c r="R25" t="n">
-        <v>33.7192</v>
+        <v>55.3435</v>
       </c>
       <c r="S25" t="n">
-        <v>4.065899999999999</v>
+        <v>-5.9504</v>
       </c>
       <c r="T25" t="n">
-        <v>3.2335</v>
+        <v>-4.7756</v>
       </c>
       <c r="U25" t="n">
-        <v>0.8321999999999999</v>
+        <v>-1.1747</v>
       </c>
       <c r="V25" t="n">
-        <v>-16.7509</v>
+        <v>-1.092400000000001</v>
       </c>
       <c r="W25" t="n">
-        <v>4.621600000000001</v>
+        <v>24.1871</v>
       </c>
       <c r="X25" t="n">
-        <v>-21.3727</v>
+        <v>-25.2794</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>J. BALFAGON MIRAVET</t>
+          <t>L. GARCIA JIMENEZ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2434,70 +2434,70 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D26" t="n">
-        <v>-60.2244</v>
+        <v>-52.8924</v>
       </c>
       <c r="E26" t="n">
-        <v>-39.1568</v>
+        <v>-46.561</v>
       </c>
       <c r="F26" t="n">
-        <v>-21.0674</v>
+        <v>-6.3314</v>
       </c>
       <c r="G26" t="n">
-        <v>-7.4504</v>
+        <v>-27.5519</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.6948</v>
+        <v>-21.4893</v>
       </c>
       <c r="I26" t="n">
-        <v>-3.755</v>
+        <v>-6.062899999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>37.6355</v>
+        <v>-7.056999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>22.3086</v>
+        <v>-5.039</v>
       </c>
       <c r="L26" t="n">
-        <v>15.3269</v>
+        <v>-2.018</v>
       </c>
       <c r="M26" t="n">
-        <v>-45.0856</v>
+        <v>-20.4953</v>
       </c>
       <c r="N26" t="n">
-        <v>-26.0036</v>
+        <v>-16.4501</v>
       </c>
       <c r="O26" t="n">
-        <v>-19.0821</v>
+        <v>-4.045100000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>-33.5361</v>
+        <v>-11.3619</v>
       </c>
       <c r="Q26" t="n">
-        <v>-88.8796</v>
+        <v>-45.0815</v>
       </c>
       <c r="R26" t="n">
-        <v>55.3435</v>
+        <v>33.7192</v>
       </c>
       <c r="S26" t="n">
-        <v>-18.1454</v>
+        <v>2.7725</v>
       </c>
       <c r="T26" t="n">
-        <v>-12.0997</v>
+        <v>0.9549999999999998</v>
       </c>
       <c r="U26" t="n">
-        <v>-6.045999999999999</v>
+        <v>1.817</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.092400000000001</v>
+        <v>-16.7509</v>
       </c>
       <c r="W26" t="n">
-        <v>24.1871</v>
+        <v>4.621600000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>-25.2794</v>
+        <v>-21.3727</v>
       </c>
     </row>
     <row r="27">
@@ -2515,22 +2515,22 @@
         <v>26</v>
       </c>
       <c r="D27" t="n">
-        <v>-283.2245</v>
+        <v>-259.3975</v>
       </c>
       <c r="E27" t="n">
-        <v>-205.8673</v>
+        <v>-196.7832</v>
       </c>
       <c r="F27" t="n">
-        <v>-77.35820000000001</v>
+        <v>-62.6137</v>
       </c>
       <c r="G27" t="n">
         <v>-178.7105</v>
       </c>
       <c r="H27" t="n">
-        <v>-79.3378</v>
+        <v>-79.33779999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>-99.37219999999999</v>
+        <v>-99.37220000000001</v>
       </c>
       <c r="J27" t="n">
         <v>102.3696</v>
@@ -2539,7 +2539,7 @@
         <v>100.3842</v>
       </c>
       <c r="L27" t="n">
-        <v>1.985300000000002</v>
+        <v>1.985300000000003</v>
       </c>
       <c r="M27" t="n">
         <v>-281.0805</v>
@@ -2560,16 +2560,16 @@
         <v>402.2497</v>
       </c>
       <c r="S27" t="n">
-        <v>-37.96729999999999</v>
+        <v>-14.1399</v>
       </c>
       <c r="T27" t="n">
-        <v>-26.03270000000001</v>
+        <v>-16.9482</v>
       </c>
       <c r="U27" t="n">
-        <v>-11.936</v>
+        <v>2.808000000000002</v>
       </c>
       <c r="V27" t="n">
-        <v>-50.96899999999999</v>
+        <v>-50.969</v>
       </c>
       <c r="W27" t="n">
         <v>135.6206</v>
